--- a/artfynd/A 34798-2024 artfynd.xlsx
+++ b/artfynd/A 34798-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73575608</v>
+        <v>56090304</v>
       </c>
       <c r="B2" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219686</v>
+        <v>1079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storön i söder, Upl</t>
+          <t>Storön, östra delen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630250.8688090181</v>
+        <v>630085</v>
       </c>
       <c r="R2" t="n">
-        <v>6706247.155934532</v>
+        <v>6706237</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-05-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-05-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>noterad</t>
+          <t>på ask</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73575609</v>
+        <v>113338865</v>
       </c>
       <c r="B3" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219686</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storön i söder, Upl</t>
+          <t>Storön i SÖ, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630105.9722552997</v>
+        <v>630083</v>
       </c>
       <c r="R3" t="n">
-        <v>6706221.214078203</v>
+        <v>6706176</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-05-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-05-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,37 +888,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96940307</v>
+        <v>113338933</v>
       </c>
       <c r="B4" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -949,19 +923,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storön i söder, Upl</t>
+          <t>Storön i SÖ, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630129.110675546</v>
+        <v>630069</v>
       </c>
       <c r="R4" t="n">
-        <v>6706196.382478714</v>
+        <v>6706244</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,22 +962,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på 4 dms ask</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,15 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113338865</v>
+        <v>56089919</v>
       </c>
       <c r="B5" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57945</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,34 +1010,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>100110</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storön i SÖ, Upl</t>
+          <t>Storön, östra delen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630083</v>
+        <v>630497</v>
       </c>
       <c r="R5" t="n">
-        <v>6706176</v>
+        <v>6706328</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,17 +1069,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2015-05-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>noterad</t>
+          <t>2015-05-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,6 +1098,728 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>73575608</v>
+      </c>
+      <c r="B6" t="n">
+        <v>107609</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storön i söder, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>630251</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6706247</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-05-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-05-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>noterad</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>73575609</v>
+      </c>
+      <c r="B7" t="n">
+        <v>107609</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storön i söder, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>630106</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6706221</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-05-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-05-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>noterad</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>56090754</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storön, östra delen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>630390</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6706250</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-08-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-08-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>56124322</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storön, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>630275</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6706006</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2014-03-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2014-03-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104729409</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storön i SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>630249</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6706016</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>56091847</v>
+      </c>
+      <c r="B11" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storön, östra delen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>630054</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6706167</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2015-07-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2015-07-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>96940307</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storön i söder, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>630129</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6706196</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-05-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-05-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34798-2024 artfynd.xlsx
+++ b/artfynd/A 34798-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090304</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113338865</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113338933</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56089919</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73575608</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73575609</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090754</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56124322</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1608,6 +1653,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104729409</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56091847</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1820,8 +1875,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96940307</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>